--- a/Datos/tabla_indicadores.xlsx
+++ b/Datos/tabla_indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/R_Projects/tablero_demografia/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D902D79B-F64C-C649-9B30-A3CEA59401D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D8F1FB-2B00-5142-B07D-28A78C347B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{DE06268A-6662-A647-A79D-6D04F0443677}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>evh</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Tasa global de fecundidad</t>
+  </si>
+  <si>
+    <t>cve_ind</t>
+  </si>
+  <si>
+    <t>nom_ind</t>
   </si>
 </sst>
 </file>
@@ -515,150 +521,158 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C3687BB-F808-5A4C-B1B7-7C08A3DEBE14}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>22</v>
       </c>
     </row>
